--- a/data/trans_dic/IP16B02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,42; 100,0</t>
+          <t>66,74; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,2; 92,77</t>
+          <t>34,74; 92,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,0; 100,0</t>
+          <t>60,17; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 100,0</t>
+          <t>62,82; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,94; 100,0</t>
+          <t>75,73; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,84; 92,98</t>
+          <t>61,02; 92,49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,45; 95,59</t>
+          <t>61,9; 95,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,45; 100,0</t>
+          <t>65,16; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,85; 96,44</t>
+          <t>71,75; 96,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73,82; 93,95</t>
+          <t>74,1; 93,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,22; 100,0</t>
+          <t>83,32; 100,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -902,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,76; 100,0</t>
+          <t>59,08; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,04; 100,0</t>
+          <t>63,59; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,21; 100,0</t>
+          <t>54,07; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,34; 96,6</t>
+          <t>73,96; 96,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,25; 100,0</t>
+          <t>44,29; 100,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,29; 100,0</t>
+          <t>46,26; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,24; 100,0</t>
+          <t>57,11; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,91; 94,32</t>
+          <t>59,37; 94,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,06; 100,0</t>
+          <t>29,44; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,42; 100,0</t>
+          <t>64,53; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,92; 94,8</t>
+          <t>58,01; 94,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,63; 97,28</t>
+          <t>74,34; 96,65</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,43; 94,04</t>
+          <t>51,12; 94,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,34 +1138,34 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,69; 100,0</t>
+          <t>31,59; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,76; 100,0</t>
+          <t>20,0; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,41; 88,83</t>
+          <t>52,43; 89,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,51; 100,0</t>
+          <t>43,69; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,27 +1243,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 84,4</t>
+          <t>16,07; 84,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,29; 100,0</t>
+          <t>62,24; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,04; 92,75</t>
+          <t>39,41; 92,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71,24; 100,0</t>
+          <t>75,92; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1274,7 +1275,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,81; 100,0</t>
+          <t>56,22; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,22; 89,6</t>
+          <t>49,06; 89,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,67; 81,87</t>
+          <t>34,33; 81,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,17; 100,0</t>
+          <t>59,66; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 100,0</t>
+          <t>47,3; 100,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,95; 96,56</t>
+          <t>68,67; 96,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,06; 90,3</t>
+          <t>62,13; 92,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,86; 84,45</t>
+          <t>45,85; 84,22</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,56; 76,46</t>
+          <t>29,69; 79,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,38; 91,27</t>
+          <t>34,88; 91,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70,92; 96,43</t>
+          <t>71,03; 96,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,06; 94,43</t>
+          <t>55,69; 94,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,39; 100,0</t>
+          <t>71,06; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,71; 86,98</t>
+          <t>60,88; 86,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,96; 89,17</t>
+          <t>58,25; 92,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87,42; 100,0</t>
+          <t>86,92; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>68,76; 88,59</t>
+          <t>67,27; 88,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,43</t>
+          <t>72,48; 87,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,84; 90,06</t>
+          <t>73,71; 90,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,33; 94,24</t>
+          <t>80,01; 94,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79,6; 92,79</t>
+          <t>79,87; 93,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,35; 96,15</t>
+          <t>83,34; 95,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,8; 90,46</t>
+          <t>79,44; 90,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>77,77; 88,87</t>
+          <t>79,11; 88,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>81,04; 91,57</t>
+          <t>80,82; 91,34</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10089</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9326</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16274</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4476; 6706</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2574; 6838</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6605; 10977</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5900; 9391</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13391; 17683</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10251; 15539</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12095</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8446</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15521</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10728</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8145</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27616</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>19174</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9087; 14027</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5932; 9103</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12507; 16808</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23796; 30177</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16523; 19831</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9427</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8993</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18421</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6498; 11000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6164; 9694</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2835</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3572; 6606</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>15305; 20004</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2885; 6514</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8158</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12764</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10231</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12381</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>22995</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3275; 7078</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5479; 9593</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9334; 14883</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1687; 5731</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9054; 14030</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8889; 14527</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>19292; 25082</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9287</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13534</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4678</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6226; 11457</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>667; 2667</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1868; 5912</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>658; 3290</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9485; 16111</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4467</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6154</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11570</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2122; 4857</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 1475</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>621; 3251</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4882; 7844</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3437; 8085</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>9345; 12310</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2265</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9045</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9631</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5284</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>18286</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>16209</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11378</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5958; 10598</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6738; 12330</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3425; 8167</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6375; 10685</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3167; 6695</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14616; 20550</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12621; 18865</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>7644; 14043</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21263</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12917</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>20409</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2677; 7132</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2215; 5794</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>13436; 18237</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>5796; 9835</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>6335; 8915</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>17005; 24246</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>9761; 15441</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>18201; 20941</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>32622</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>63680</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>51613</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>52148</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>84770</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>128920</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>98649</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>27316; 36076</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>57051; 68588</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>45684; 55848</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>46984; 55411</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>59559; 69537</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>43068; 49505</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>78912; 89573</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>121270; 136264</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>91854; 103806</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Provincia-trans_dic.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,74; 100,0</t>
+          <t>63,99; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 92,29</t>
+          <t>43,41; 92,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,17; 100,0</t>
+          <t>65,34; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,82; 100,0</t>
+          <t>63,06; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,73; 100,0</t>
+          <t>76,62; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,02; 92,49</t>
+          <t>59,57; 92,76</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,9; 95,55</t>
+          <t>60,46; 95,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,16; 100,0</t>
+          <t>64,78; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,75; 96,43</t>
+          <t>70,45; 96,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74,1; 93,98</t>
+          <t>73,9; 93,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,32; 100,0</t>
+          <t>83,52; 100,0</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,08; 100,0</t>
+          <t>58,12; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,59; 100,0</t>
+          <t>69,62; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>23,73; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,96; 96,66</t>
+          <t>70,56; 96,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,29; 100,0</t>
+          <t>41,93; 100,0</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,26; 100,0</t>
+          <t>52,67; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,11; 100,0</t>
+          <t>55,18; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,37; 94,67</t>
+          <t>61,0; 94,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 100,0</t>
+          <t>30,88; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,53; 100,0</t>
+          <t>64,79; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,01; 94,79</t>
+          <t>59,21; 94,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,34; 96,65</t>
+          <t>74,23; 96,9</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,12; 94,07</t>
+          <t>51,67; 93,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,0; 100,0</t>
+          <t>19,76; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,43; 89,06</t>
+          <t>53,83; 88,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,69; 100,0</t>
+          <t>42,76; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,07; 84,15</t>
+          <t>16,09; 93,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,24; 100,0</t>
+          <t>62,35; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,41; 92,72</t>
+          <t>46,65; 92,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,92; 100,0</t>
+          <t>75,67; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,22; 100,0</t>
+          <t>57,25; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,06; 89,77</t>
+          <t>45,13; 88,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,33; 81,85</t>
+          <t>33,33; 82,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59,66; 100,0</t>
+          <t>59,9; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,22 +1363,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,3; 100,0</t>
+          <t>46,29; 100,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,67; 96,55</t>
+          <t>66,07; 96,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,13; 92,87</t>
+          <t>62,62; 90,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,85; 84,22</t>
+          <t>47,89; 85,19</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,69; 79,09</t>
+          <t>27,83; 78,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,88; 91,25</t>
+          <t>32,69; 91,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,32 +1463,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71,03; 96,41</t>
+          <t>70,33; 96,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,69; 94,5</t>
+          <t>54,99; 94,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,06; 100,0</t>
+          <t>69,19; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,88; 86,8</t>
+          <t>62,12; 87,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,25; 92,15</t>
+          <t>59,16; 92,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>86,92; 100,0</t>
+          <t>85,25; 100,0</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>67,27; 88,84</t>
+          <t>68,48; 88,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,48; 87,14</t>
+          <t>72,72; 87,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,71; 90,11</t>
+          <t>74,2; 89,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,01; 94,36</t>
+          <t>82,08; 94,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79,87; 93,25</t>
+          <t>79,63; 93,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,79</t>
+          <t>82,2; 96,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,44; 90,18</t>
+          <t>78,57; 90,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>79,11; 88,9</t>
+          <t>78,87; 88,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80,82; 91,34</t>
+          <t>80,87; 91,38</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4476; 6706</t>
+          <t>4291; 6706</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2574; 6838</t>
+          <t>3216; 6848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6605; 10977</t>
+          <t>7173; 10977</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5900; 9391</t>
+          <t>5922; 9391</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13391; 17683</t>
+          <t>13549; 17683</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10251; 15539</t>
+          <t>10008; 15583</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9087; 14027</t>
+          <t>8877; 14034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5932; 9103</t>
+          <t>5897; 9103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12507; 16808</t>
+          <t>12279; 16806</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23796; 30177</t>
+          <t>23729; 30168</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16523; 19831</t>
+          <t>16563; 19831</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6498; 11000</t>
+          <t>6394; 11000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6164; 9694</t>
+          <t>6749; 9694</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>673; 2835</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15305; 20004</t>
+          <t>14602; 19988</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2885; 6514</t>
+          <t>2731; 6514</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2350,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3275; 7078</t>
+          <t>3728; 7078</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5479; 9593</t>
+          <t>5293; 9593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9334; 14883</t>
+          <t>9590; 14928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1687; 5731</t>
+          <t>1770; 5731</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9054; 14030</t>
+          <t>9090; 14030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8889; 14527</t>
+          <t>9073; 14508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19292; 25082</t>
+          <t>19265; 25148</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6226; 11457</t>
+          <t>6293; 11428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>658; 3290</t>
+          <t>650; 3290</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9485; 16111</t>
+          <t>9738; 16007</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2122; 4857</t>
+          <t>2077; 4857</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>621; 3251</t>
+          <t>622; 3629</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4882; 7844</t>
+          <t>4890; 7844</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3437; 8085</t>
+          <t>4067; 8100</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9345; 12310</t>
+          <t>9315; 12310</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,22 +2839,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5958; 10598</t>
+          <t>6068; 10598</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6738; 12330</t>
+          <t>6199; 12172</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3425; 8167</t>
+          <t>3326; 8200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6375; 10685</t>
+          <t>6401; 10685</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2864,22 +2864,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3167; 6695</t>
+          <t>3099; 6695</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14616; 20550</t>
+          <t>14061; 20451</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12621; 18865</t>
+          <t>12721; 18356</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7644; 14043</t>
+          <t>7985; 14204</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2677; 7132</t>
+          <t>2509; 7067</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2215; 5794</t>
+          <t>2076; 5808</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,32 +3017,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13436; 18237</t>
+          <t>13302; 18231</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5796; 9835</t>
+          <t>5723; 9797</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6335; 8915</t>
+          <t>6168; 8915</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17005; 24246</t>
+          <t>17350; 24393</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9761; 15441</t>
+          <t>9913; 15499</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18201; 20941</t>
+          <t>17853; 20941</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27316; 36076</t>
+          <t>27806; 36010</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>57051; 68588</t>
+          <t>57235; 68961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45684; 55848</t>
+          <t>45988; 55696</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46984; 55411</t>
+          <t>48201; 55538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59559; 69537</t>
+          <t>59379; 69492</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43068; 49505</t>
+          <t>42480; 49702</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78912; 89573</t>
+          <t>78049; 89912</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>121270; 136264</t>
+          <t>120894; 135732</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91854; 103806</t>
+          <t>91907; 103862</t>
         </is>
       </c>
     </row>
